--- a/fhir/StructureDefinition-ehealth-questionnaire-advanced.xlsx
+++ b/fhir/StructureDefinition-ehealth-questionnaire-advanced.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>9.0.1</t>
+    <t>10.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-23T08:01:32+00:00</t>
+    <t>2026-08-06T13:29:38+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -359,7 +359,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -782,7 +782,7 @@
     <t>Questionnaire.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(Questionnaire)
+    <t xml:space="preserve">canonical(Questionnaire|4.0.1)
 </t>
   </si>
   <si>
@@ -1142,7 +1142,7 @@
     <t>Codes for questionnaires, groups and individual questions.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/questionnaire-questions</t>
+    <t>http://hl7.org/fhir/ValueSet/questionnaire-questions|4.0.1</t>
   </si>
   <si>
     <t>.code</t>
@@ -1680,7 +1680,7 @@
     <t>String equivalent with html markup</t>
   </si>
   <si>
-    <t>This is an equivalent of the string on which the extension is sent, but includes additional XHTML markup, such as bold, italics, styles, tables, etc. Existing [restrictions on XHTML content](http://hl7.org/fhir/R4/narrative.html#security) apply. Note that using [markdown](http://hl7.org/fhir/extensions/5.3.0-ballot-tc1/StructureDefinition-rendering-markdown.html) allows for greater flexibility of display.</t>
+    <t>This is an equivalent of the string on which the extension is sent, but includes additional XHTML markup, such as bold, italics, styles, tables, etc. Existing [restrictions on XHTML content](http://hl7.org/fhir/R4/narrative.html#security) apply. Note that using [markdown](http://hl7.org/fhir/extensions/5.3.0/StructureDefinition-rendering-markdown.html) allows for greater flexibility of display.</t>
   </si>
   <si>
     <t>For questionnaires, see additional guidance and examples in the [SDC implementation guide](http://hl7.org/fhir/uv/sdc/2025Jan/rendering.html#rendering-xhtml).</t>
@@ -1790,7 +1790,7 @@
   </si>
   <si>
     <t>boolean
-decimalintegerdatedateTimetimestringCodingQuantityReference(Resource)</t>
+decimalintegerdatedateTimetimestringCodingQuantityReference(Resource|4.0.1)</t>
   </si>
   <si>
     <t>Value for question comparison based on operator</t>
@@ -1802,7 +1802,7 @@
     <t>Allowed values to answer questions.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/questionnaire-answers</t>
+    <t>http://hl7.org/fhir/ValueSet/questionnaire-answers|4.0.1</t>
   </si>
   <si>
     <t xml:space="preserve">que-7
@@ -1937,7 +1937,7 @@
     <t>Questionnaire.item.answerValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ValueSet)
+    <t xml:space="preserve">canonical(ValueSet|4.0.1)
 </t>
   </si>
   <si>
@@ -2006,7 +2006,7 @@
   </si>
   <si>
     <t>integer
-datetimestringCodingReference(Resource)</t>
+datetimestringCodingReference(Resource|4.0.1)</t>
   </si>
   <si>
     <t>Answer value</t>
@@ -2074,7 +2074,7 @@
   </si>
   <si>
     <t>boolean
-decimalintegerdatedateTimetimestringuriAttachmentCodingQuantityReference(Resource)</t>
+decimalintegerdatedateTimetimestringuriAttachmentCodingQuantityReference(Resource|4.0.1)</t>
   </si>
   <si>
     <t>Actual value for initializing the question</t>

--- a/fhir/StructureDefinition-ehealth-questionnaire-advanced.xlsx
+++ b/fhir/StructureDefinition-ehealth-questionnaire-advanced.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.0</t>
+    <t>10.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-06T13:29:38+00:00</t>
+    <t>2026-08-11T06:44:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-questionnaire-advanced.xlsx
+++ b/fhir/StructureDefinition-ehealth-questionnaire-advanced.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.1</t>
+    <t>10.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-11T06:44:23+00:00</t>
+    <t>2026-09-10T10:12:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-questionnaire-advanced.xlsx
+++ b/fhir/StructureDefinition-ehealth-questionnaire-advanced.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>10.0.2</t>
+    <t>11.0.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T10:12:06+00:00</t>
+    <t>2026-10-21T13:41:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-questionnaire-advanced.xlsx
+++ b/fhir/StructureDefinition-ehealth-questionnaire-advanced.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.0</t>
+    <t>11.0.1</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-21T13:41:32+00:00</t>
+    <t>2026-10-23T09:30:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/fhir/StructureDefinition-ehealth-questionnaire-advanced.xlsx
+++ b/fhir/StructureDefinition-ehealth-questionnaire-advanced.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.1</t>
+    <t>11.0.2</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-23T09:30:26+00:00</t>
+    <t>2026-10-29T09:18:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1680,7 +1680,7 @@
     <t>String equivalent with html markup</t>
   </si>
   <si>
-    <t>This is an equivalent of the string on which the extension is sent, but includes additional XHTML markup, such as bold, italics, styles, tables, etc. Existing [restrictions on XHTML content](http://hl7.org/fhir/R4/narrative.html#security) apply. Note that using [markdown](http://hl7.org/fhir/extensions/5.3.0/StructureDefinition-rendering-markdown.html) allows for greater flexibility of display.</t>
+    <t>This is an equivalent of the string on which the extension is sent, but includes additional XHTML markup, such as bold, italics, styles, tables, etc. Existing [restrictions on XHTML content](http://hl7.org/fhir/R4/narrative.html#security) apply. Note that using [markdown](http://hl7.org/fhir/extensions/5.4.0/StructureDefinition-rendering-markdown.html) allows for greater flexibility of display.</t>
   </si>
   <si>
     <t>For questionnaires, see additional guidance and examples in the [SDC implementation guide](http://hl7.org/fhir/uv/sdc/2025Jan/rendering.html#rendering-xhtml).</t>

--- a/fhir/StructureDefinition-ehealth-questionnaire-advanced.xlsx
+++ b/fhir/StructureDefinition-ehealth-questionnaire-advanced.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>11.0.2</t>
+    <t>11.0.3</t>
   </si>
   <si>
     <t>Name</t>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-29T09:18:06+00:00</t>
+    <t>2026-10-29T11:52:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
